--- a/artfynd/A 31164-2025 artfynd.xlsx
+++ b/artfynd/A 31164-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>127155066</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31164-2025 artfynd.xlsx
+++ b/artfynd/A 31164-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>127155066</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31164-2025 artfynd.xlsx
+++ b/artfynd/A 31164-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127155126</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127155066</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31164-2025 artfynd.xlsx
+++ b/artfynd/A 31164-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127155126</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127155066</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31164-2025 artfynd.xlsx
+++ b/artfynd/A 31164-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127155126</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127155066</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31164-2025 artfynd.xlsx
+++ b/artfynd/A 31164-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127155126</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127155066</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31164-2025 artfynd.xlsx
+++ b/artfynd/A 31164-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127155126</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127155066</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31164-2025 artfynd.xlsx
+++ b/artfynd/A 31164-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,46 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127155126</v>
+        <v>127154796</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466040</v>
+        <v>466096</v>
       </c>
       <c r="R2" t="n">
-        <v>6809191</v>
+        <v>6809177</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,11 +779,11 @@
         <v>127155066</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -883,6 +875,444 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127154687</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>466105</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6809170</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127155126</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>466040</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6809191</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127155380</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>466021</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6809226</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127154682</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>466105</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6809170</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31164-2025 artfynd.xlsx
+++ b/artfynd/A 31164-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154796</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155066</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154687</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155126</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155380</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,8 +1342,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154682</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>